--- a/artfynd/A 2661-2026 artfynd.xlsx
+++ b/artfynd/A 2661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136213793</v>
       </c>
       <c r="B2" t="n">
-        <v>98363</v>
+        <v>98366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136297319</v>
       </c>
       <c r="B3" t="n">
-        <v>99380</v>
+        <v>99383</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136213276</v>
       </c>
       <c r="B4" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136213789</v>
       </c>
       <c r="B5" t="n">
-        <v>98421</v>
+        <v>98424</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136213342</v>
       </c>
       <c r="B6" t="n">
-        <v>99619</v>
+        <v>99622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136213752</v>
       </c>
       <c r="B7" t="n">
-        <v>98393</v>
+        <v>98396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 2661-2026 artfynd.xlsx
+++ b/artfynd/A 2661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136213793</v>
       </c>
       <c r="B2" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136297319</v>
       </c>
       <c r="B3" t="n">
-        <v>99383</v>
+        <v>99384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136213276</v>
       </c>
       <c r="B4" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136213789</v>
       </c>
       <c r="B5" t="n">
-        <v>98424</v>
+        <v>98425</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136213342</v>
       </c>
       <c r="B6" t="n">
-        <v>99622</v>
+        <v>99623</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136213752</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>98397</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 2661-2026 artfynd.xlsx
+++ b/artfynd/A 2661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136213793</v>
       </c>
       <c r="B2" t="n">
-        <v>98367</v>
+        <v>98372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136297319</v>
       </c>
       <c r="B3" t="n">
-        <v>99384</v>
+        <v>99389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136213276</v>
       </c>
       <c r="B4" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136213789</v>
       </c>
       <c r="B5" t="n">
-        <v>98425</v>
+        <v>98430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136213342</v>
       </c>
       <c r="B6" t="n">
-        <v>99623</v>
+        <v>99628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136213752</v>
       </c>
       <c r="B7" t="n">
-        <v>98397</v>
+        <v>98402</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 2661-2026 artfynd.xlsx
+++ b/artfynd/A 2661-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136213793</v>
       </c>
       <c r="B2" t="n">
-        <v>98372</v>
+        <v>98374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136297319</v>
       </c>
       <c r="B3" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136213276</v>
       </c>
       <c r="B4" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136213789</v>
       </c>
       <c r="B5" t="n">
-        <v>98430</v>
+        <v>98432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136213342</v>
       </c>
       <c r="B6" t="n">
-        <v>99628</v>
+        <v>99630</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136213752</v>
       </c>
       <c r="B7" t="n">
-        <v>98402</v>
+        <v>98404</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
